--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -1,45 +1,526 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="19200" windowHeight="6800"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DSA Metadata" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$13</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>Find the Second Largest Element in an Array</t>
+  </si>
+  <si>
+    <t>Array traversal</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>Reverse an Array</t>
+  </si>
+  <si>
+    <t>Two pointers / in-place swap</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>Check if an Array is Sorted in Ascending Order</t>
+  </si>
+  <si>
+    <t>Array traversal / adjacent comparison</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>Find the Missing Number in an Array</t>
+  </si>
+  <si>
+    <t>Array / sum formula</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>Move All Zeros to the End</t>
+  </si>
+  <si>
+    <t>Array / order preservation</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>Find Duplicate Elements</t>
+  </si>
+  <si>
+    <t>Nested loops / occurrence checking</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>Two Sum</t>
+  </si>
+  <si>
+    <t>Nested loops / pair searching</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>Find the First Non-Repeating Element</t>
+  </si>
+  <si>
+    <t>Nested loops / counting occurrences</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>Find the Majority Element</t>
+  </si>
+  <si>
+    <t>Counting occurrences / threshold</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>Find the Second Largest Unique Element</t>
+  </si>
+  <si>
+    <t>Array traversal / duplicate handling</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>Remove Duplicates from a Sorted Array</t>
+  </si>
+  <si>
+    <t>Sorted array / single traversal</t>
+  </si>
+  <si>
+    <t>Find the Element with the Highest Frequency</t>
+  </si>
+  <si>
+    <t>Hash Map / Dictionary &amp; Frequency Counting</t>
+  </si>
+  <si>
+    <t>Find the First Repeating Element</t>
+  </si>
+  <si>
+    <t>Set / Hashing &amp; Duplicate Detection</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -47,91 +528,327 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -414,269 +1131,222 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:4">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Find the Second Largest Element in an Array</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Array traversal</t>
-        </is>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:4">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Reverse an Array</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Two pointers / in-place swap</t>
-        </is>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:4">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Check if an Array is Sorted in Ascending Order</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Array traversal / adjacent comparison</t>
-        </is>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:4">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Find the Missing Number in an Array</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Array / sum formula</t>
-        </is>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:4">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Move All Zeros to the End</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Array / order preservation</t>
-        </is>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:4">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Find Duplicate Elements</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Nested loops / occurrence checking</t>
-        </is>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:4">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Two Sum</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Nested loops / pair searching</t>
-        </is>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+    <row r="9" spans="1:4">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Find the First Non-Repeating Element</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Nested loops / counting occurrences</t>
-        </is>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:4">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Find the Majority Element</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Counting occurrences / threshold</t>
-        </is>
+      <c r="B10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:4">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Find the Second Largest Unique Element</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Array traversal / duplicate handling</t>
-        </is>
+      <c r="B11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:4">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Remove Duplicates from a Sorted Array</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Sorted array / single traversal</t>
-        </is>
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46279</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46280</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D12"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D13" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Day</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t>Set / Hashing &amp; Duplicate Detection</t>
+  </si>
+  <si>
+    <t>Move All Negative Numbers to One Side</t>
+  </si>
+  <si>
+    <t>Two Pointers / Partitioning</t>
   </si>
 </sst>
 </file>
@@ -166,7 +172,7 @@
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +186,12 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -644,137 +656,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -790,6 +802,9 @@
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1137,7 +1152,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1332,7 +1347,7 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="3">
         <v>46280</v>
       </c>
       <c r="C14" t="s">
@@ -1342,8 +1357,22 @@
         <v>40</v>
       </c>
     </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46281</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D13" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D14" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Day</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>Two Pointers / Partitioning</t>
+  </si>
+  <si>
+    <t>Find the Longest Consecutive Sequence</t>
+  </si>
+  <si>
+    <t>Nested Loops / Array Traversal &amp; Consecutive Sequence</t>
   </si>
 </sst>
 </file>
@@ -800,11 +806,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1152,7 +1158,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1361,18 +1367,32 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="3">
         <v>46281</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>41</v>
       </c>
       <c r="D15" t="s">
         <v>42</v>
       </c>
     </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6">
+        <v>46282</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D14" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D15" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Day</t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>Nested Loops / Array Traversal &amp; Consecutive Sequence</t>
+  </si>
+  <si>
+    <t>Find the Intersection of Two Arrays</t>
+  </si>
+  <si>
+    <t>Nested Loops / Array Comparison &amp; Duplicate Handling</t>
   </si>
 </sst>
 </file>
@@ -792,7 +798,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -811,6 +817,9 @@
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1158,7 +1167,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1381,7 +1390,7 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="3">
         <v>46282</v>
       </c>
       <c r="C16" t="s">
@@ -1391,8 +1400,22 @@
         <v>44</v>
       </c>
     </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6">
+        <v>46283</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D15" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D16" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Day</t>
   </si>
@@ -171,6 +171,12 @@
   </si>
   <si>
     <t>Nested Loops / Array Comparison &amp; Duplicate Handling</t>
+  </si>
+  <si>
+    <t>Find the Pair with the Maximum Sum</t>
+  </si>
+  <si>
+    <t>Array Traversal / Largest &amp; Second Largest</t>
   </si>
 </sst>
 </file>
@@ -798,7 +804,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -817,9 +823,6 @@
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1167,7 +1170,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1404,18 +1407,32 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="3">
         <v>46283</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D17" t="s">
         <v>46</v>
       </c>
     </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6">
+        <v>46284</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D16" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D17" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>Day</t>
   </si>
@@ -177,6 +177,12 @@
   </si>
   <si>
     <t>Array Traversal / Largest &amp; Second Largest</t>
+  </si>
+  <si>
+    <t>Find the Pair with the Given Difference</t>
+  </si>
+  <si>
+    <t>Nested Loops / Pair Comparison &amp; Absolute Difference</t>
   </si>
 </sst>
 </file>
@@ -190,7 +196,7 @@
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,6 +216,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -674,137 +688,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -823,6 +837,12 @@
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1170,7 +1190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1421,7 +1441,7 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="3">
         <v>46284</v>
       </c>
       <c r="C18" t="s">
@@ -1431,8 +1451,25 @@
         <v>48</v>
       </c>
     </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6">
+        <v>46285</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="8"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D17" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D18" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Day</t>
   </si>
@@ -183,6 +183,12 @@
   </si>
   <si>
     <t>Nested Loops / Pair Comparison &amp; Absolute Difference</t>
+  </si>
+  <si>
+    <t>Find the Missing Number Using XOR</t>
+  </si>
+  <si>
+    <t>XOR / Bitwise Operations &amp; Array Traversal</t>
   </si>
 </sst>
 </file>
@@ -196,7 +202,7 @@
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,14 +222,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -688,137 +686,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -835,14 +833,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1455,21 +1450,32 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="3">
         <v>46285</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D19" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:3">
-      <c r="C20" s="8"/>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7">
+        <v>46286</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D18" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D19" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Day</t>
   </si>
@@ -189,6 +189,12 @@
   </si>
   <si>
     <t>XOR / Bitwise Operations &amp; Array Traversal</t>
+  </si>
+  <si>
+    <t>Reverse a Singly Linked List</t>
+  </si>
+  <si>
+    <t>Singly Linked List / Pointer Manipulation / Three-Pointer Technique</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1191,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1464,7 +1470,7 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="3">
         <v>46286</v>
       </c>
       <c r="C20" t="s">
@@ -1474,8 +1480,22 @@
         <v>52</v>
       </c>
     </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7">
+        <v>46287</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D19" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D20" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>Day</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>Singly Linked List / Pointer Manipulation / Three-Pointer Technique</t>
+  </si>
+  <si>
+    <t>Find the Middle Element of a Singly Linked List</t>
+  </si>
+  <si>
+    <t>Singly Linked List / Pointer Traversal / Node Counting</t>
   </si>
 </sst>
 </file>
@@ -1191,7 +1197,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1484,7 +1490,7 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="3">
         <v>46287</v>
       </c>
       <c r="C21" t="s">
@@ -1494,8 +1500,22 @@
         <v>54</v>
       </c>
     </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7">
+        <v>46288</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D20" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D21" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Day</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>Singly Linked List / Pointer Traversal / Node Counting</t>
+  </si>
+  <si>
+    <t>Detect a Cycle in a Singly Linked List</t>
+  </si>
+  <si>
+    <t>Two Pointers / Floyd’s Cycle Detection / Pointer Traversal</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1203,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1504,7 +1510,7 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="3">
         <v>46288</v>
       </c>
       <c r="C22" t="s">
@@ -1514,8 +1520,22 @@
         <v>56</v>
       </c>
     </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46289</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D21" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D22" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Day</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>Two Pointers / Floyd’s Cycle Detection / Pointer Traversal</t>
+  </si>
+  <si>
+    <t>Find the Longest Subarray with Sum K</t>
+  </si>
+  <si>
+    <t>Nested Loops / Running Sum / Subarray Traversal / Maximum Length</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1209,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1524,7 +1530,7 @@
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="3">
         <v>46289</v>
       </c>
       <c r="C23" t="s">
@@ -1534,8 +1540,22 @@
         <v>58</v>
       </c>
     </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46290</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D22" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D23" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>Day</t>
   </si>
@@ -213,6 +213,12 @@
   </si>
   <si>
     <t>Nested Loops / Running Sum / Subarray Traversal / Maximum Length</t>
+  </si>
+  <si>
+    <t>Find the Maximum Consecutive 1s</t>
+  </si>
+  <si>
+    <t>Array Traversal / Counting / Running Count /Maximum value</t>
   </si>
 </sst>
 </file>
@@ -840,7 +846,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -862,6 +868,9 @@
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1209,7 +1218,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1544,7 +1553,7 @@
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="3">
         <v>46290</v>
       </c>
       <c r="C24" t="s">
@@ -1554,8 +1563,22 @@
         <v>60</v>
       </c>
     </row>
+    <row r="25" ht="29" spans="1:4">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46291</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D23" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D24" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>Day</t>
   </si>
@@ -219,6 +219,12 @@
   </si>
   <si>
     <t>Array Traversal / Counting / Running Count /Maximum value</t>
+  </si>
+  <si>
+    <t>Find the Longest Increasing Subarray</t>
+  </si>
+  <si>
+    <t>Array Traversal / Adjacent Comparison / Running Count / Maximum Length</t>
   </si>
 </sst>
 </file>
@@ -866,11 +872,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1218,7 +1224,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1567,18 +1573,32 @@
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="3">
         <v>46291</v>
       </c>
       <c r="C25" t="s">
         <v>61</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>62</v>
       </c>
     </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8">
+        <v>46292</v>
+      </c>
+      <c r="C26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D24" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D25" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>Day</t>
   </si>
@@ -225,6 +225,12 @@
   </si>
   <si>
     <t>Array Traversal / Adjacent Comparison / Running Count / Maximum Length</t>
+  </si>
+  <si>
+    <t>Find the First Missing Positive</t>
+  </si>
+  <si>
+    <t>Nested Loops / Array Traversal / Searching / Boolean Flag</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1230,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1587,7 +1593,7 @@
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="3">
         <v>46292</v>
       </c>
       <c r="C26" t="s">
@@ -1597,8 +1603,22 @@
         <v>64</v>
       </c>
     </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46293</v>
+      </c>
+      <c r="C27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D25" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D26" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Day</t>
   </si>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>Nested Loops / Array Traversal / Searching / Boolean Flag</t>
+  </si>
+  <si>
+    <t>Find the Equilibrium Index</t>
+  </si>
+  <si>
+    <t>Prefix Sum / Left Sum / Right Sum / Array Traversal</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1236,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1607,7 +1613,7 @@
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="3">
         <v>46293</v>
       </c>
       <c r="C27" t="s">
@@ -1617,8 +1623,22 @@
         <v>66</v>
       </c>
     </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8">
+        <v>46294</v>
+      </c>
+      <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D26" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D27" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Day</t>
   </si>
@@ -237,6 +237,12 @@
   </si>
   <si>
     <t>Prefix Sum / Left Sum / Right Sum / Array Traversal</t>
+  </si>
+  <si>
+    <t>Find the Maximum Difference Between Two Elements</t>
+  </si>
+  <si>
+    <t>Array Traversal / Minimum Element So Far / Maximum Difference / Greedy Approach</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1242,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1627,7 +1633,7 @@
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="3">
         <v>46294</v>
       </c>
       <c r="C28" t="s">
@@ -1637,8 +1643,22 @@
         <v>68</v>
       </c>
     </row>
+    <row r="29" spans="1:4">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46295</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D27" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D28" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t>Day</t>
   </si>
@@ -243,6 +243,12 @@
   </si>
   <si>
     <t>Array Traversal / Minimum Element So Far / Maximum Difference / Greedy Approach</t>
+  </si>
+  <si>
+    <t>Find the First Element That Appears Twice</t>
+  </si>
+  <si>
+    <t>Nested Loops / Duplicate Detection / Index Tracking</t>
   </si>
 </sst>
 </file>
@@ -870,7 +876,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -895,6 +901,9 @@
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1242,7 +1251,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1647,7 +1656,7 @@
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="3">
         <v>46295</v>
       </c>
       <c r="C29" t="s">
@@ -1657,8 +1666,25 @@
         <v>70</v>
       </c>
     </row>
+    <row r="30" ht="29" spans="1:4">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46296</v>
+      </c>
+      <c r="C30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="4:4">
+      <c r="D31" s="9"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D28" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D29" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>Day</t>
   </si>
@@ -249,6 +249,12 @@
   </si>
   <si>
     <t>Nested Loops / Duplicate Detection / Index Tracking</t>
+  </si>
+  <si>
+    <t>Find the Longest Subarray with Equal Number of 0s and 1s</t>
+  </si>
+  <si>
+    <t>Arrays / Subarrays / Nested Loops / Counting</t>
   </si>
 </sst>
 </file>
@@ -876,7 +882,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -901,9 +907,6 @@
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1670,21 +1673,32 @@
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="3">
         <v>46296</v>
       </c>
       <c r="C30" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="4:4">
-      <c r="D31" s="9"/>
+    <row r="31" spans="1:4">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46297</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D29" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D30" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>Day</t>
   </si>
@@ -255,6 +255,12 @@
   </si>
   <si>
     <t>Arrays / Subarrays / Nested Loops / Counting</t>
+  </si>
+  <si>
+    <t>Find the Maximum Product of Two Elements in an Array</t>
+  </si>
+  <si>
+    <t>Arrays / Nested Loops / Pair Comparison</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1687,7 +1693,7 @@
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="3">
         <v>46297</v>
       </c>
       <c r="C31" t="s">
@@ -1697,8 +1703,22 @@
         <v>74</v>
       </c>
     </row>
+    <row r="32" spans="1:4">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46298</v>
+      </c>
+      <c r="C32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D30" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D31" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>Day</t>
   </si>
@@ -261,6 +261,12 @@
   </si>
   <si>
     <t>Arrays / Nested Loops / Pair Comparison</t>
+  </si>
+  <si>
+    <t>Rotate an Array to the Right by K Positions</t>
+  </si>
+  <si>
+    <t>Arrays / Array Rotation / List Operations</t>
   </si>
 </sst>
 </file>
@@ -888,7 +894,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -913,6 +919,9 @@
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1260,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1707,7 +1716,7 @@
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="3">
         <v>46298</v>
       </c>
       <c r="C32" t="s">
@@ -1717,8 +1726,22 @@
         <v>76</v>
       </c>
     </row>
+    <row r="33" spans="1:4">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46299</v>
+      </c>
+      <c r="C33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D31" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D32" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>Day</t>
   </si>
@@ -267,6 +267,12 @@
   </si>
   <si>
     <t>Arrays / Array Rotation / List Operations</t>
+  </si>
+  <si>
+    <t>Merge Two Sorted Arrays</t>
+  </si>
+  <si>
+    <t>Arrays / Two Pointers / Array Merging</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1275,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1730,18 +1736,32 @@
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="3">
         <v>46299</v>
       </c>
       <c r="C33" t="s">
         <v>77</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="6" t="s">
         <v>78</v>
       </c>
     </row>
+    <row r="34" spans="1:4">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46300</v>
+      </c>
+      <c r="C34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D32" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D33" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>Day</t>
   </si>
@@ -273,6 +273,12 @@
   </si>
   <si>
     <t>Arrays / Two Pointers / Array Merging</t>
+  </si>
+  <si>
+    <t>Apply a Quick Sort</t>
+  </si>
+  <si>
+    <t>Arrays / Recursion</t>
   </si>
 </sst>
 </file>
@@ -900,7 +906,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -925,9 +931,6 @@
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1275,7 +1278,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1750,18 +1753,32 @@
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="3">
         <v>46300</v>
       </c>
       <c r="C34" t="s">
         <v>79</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="6" t="s">
         <v>80</v>
       </c>
     </row>
+    <row r="35" spans="1:4">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46301</v>
+      </c>
+      <c r="C35" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D33" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D34" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>Day</t>
   </si>
@@ -279,6 +279,12 @@
   </si>
   <si>
     <t>Arrays / Recursion</t>
+  </si>
+  <si>
+    <t>Check for Valid Parentheses</t>
+  </si>
+  <si>
+    <t>Stack / Parentheses Matching / LIFO / Push and Pop</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1284,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1767,7 +1773,7 @@
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="3">
         <v>46301</v>
       </c>
       <c r="C35" t="s">
@@ -1777,8 +1783,22 @@
         <v>82</v>
       </c>
     </row>
+    <row r="36" spans="1:4">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46302</v>
+      </c>
+      <c r="C36" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D34" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D35" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>Day</t>
   </si>
@@ -285,6 +285,12 @@
   </si>
   <si>
     <t>Stack / Parentheses Matching / LIFO / Push and Pop</t>
+  </si>
+  <si>
+    <t>Evaluate Postfix Expression Using Stack</t>
+  </si>
+  <si>
+    <t>Stack / Postfix Evaluation / LIFO / Push and Pop</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1290,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1787,7 +1793,7 @@
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="3">
         <v>46302</v>
       </c>
       <c r="C36" t="s">
@@ -1797,8 +1803,22 @@
         <v>84</v>
       </c>
     </row>
+    <row r="37" spans="1:4">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46303</v>
+      </c>
+      <c r="C37" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D35" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D36" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>Day</t>
   </si>
@@ -291,6 +291,12 @@
   </si>
   <si>
     <t>Stack / Postfix Evaluation / LIFO / Push and Pop</t>
+  </si>
+  <si>
+    <t>Infix to Postfix Conversion Using Stack</t>
+  </si>
+  <si>
+    <t>Stack / Operator Precedence / Associativity / Parentheses</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1296,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1807,7 +1813,7 @@
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="3">
         <v>46303</v>
       </c>
       <c r="C37" t="s">
@@ -1817,8 +1823,22 @@
         <v>86</v>
       </c>
     </row>
+    <row r="38" spans="1:4">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46304</v>
+      </c>
+      <c r="C38" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D36" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D37" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>Day</t>
   </si>
@@ -297,6 +297,12 @@
   </si>
   <si>
     <t>Stack / Operator Precedence / Associativity / Parentheses</t>
+  </si>
+  <si>
+    <t>Product of Array Except Self</t>
+  </si>
+  <si>
+    <t>Arrays / Nested Loops / Brute Force / Time Complexity Optimization</t>
   </si>
 </sst>
 </file>
@@ -1296,7 +1302,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1827,7 +1833,7 @@
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="3">
         <v>46304</v>
       </c>
       <c r="C38" t="s">
@@ -1837,8 +1843,32 @@
         <v>88</v>
       </c>
     </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46307</v>
+      </c>
+      <c r="C41" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D37" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D38" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>Day</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>Arrays / Nested Loops / Brute Force / Time Complexity Optimization</t>
+  </si>
+  <si>
+    <t>Check Whether a String Is Palindrome Using Stack</t>
+  </si>
+  <si>
+    <t>String / Stack / LIFO / String Reversal</t>
   </si>
 </sst>
 </file>
@@ -1302,7 +1308,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1857,7 +1863,7 @@
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="3">
         <v>46307</v>
       </c>
       <c r="C41" t="s">
@@ -1867,8 +1873,22 @@
         <v>90</v>
       </c>
     </row>
+    <row r="42" spans="1:4">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46308</v>
+      </c>
+      <c r="C42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D38" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D41" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>Day</t>
   </si>
@@ -309,6 +309,12 @@
   </si>
   <si>
     <t>String / Stack / LIFO / String Reversal</t>
+  </si>
+  <si>
+    <t>Median of Two Sorted Arrays</t>
+  </si>
+  <si>
+    <t>Arrays / Sorting / Quick Sort / Median</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1314,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1877,7 +1883,7 @@
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="3">
         <v>46308</v>
       </c>
       <c r="C42" t="s">
@@ -1887,8 +1893,22 @@
         <v>92</v>
       </c>
     </row>
+    <row r="43" spans="1:4">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46309</v>
+      </c>
+      <c r="C43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D41" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D42" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>Day</t>
   </si>
@@ -315,6 +315,12 @@
   </si>
   <si>
     <t>Arrays / Sorting / Quick Sort / Median</t>
+  </si>
+  <si>
+    <t>Reverse Integer</t>
+  </si>
+  <si>
+    <t>Math / Digit Manipulation / Overflow Handling</t>
   </si>
 </sst>
 </file>
@@ -942,7 +948,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -967,6 +973,9 @@
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1314,7 +1323,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1897,7 +1906,7 @@
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="3">
         <v>46309</v>
       </c>
       <c r="C43" t="s">
@@ -1907,8 +1916,22 @@
         <v>94</v>
       </c>
     </row>
+    <row r="44" spans="1:4">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46310</v>
+      </c>
+      <c r="C44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D42" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D43" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>Day</t>
   </si>
@@ -321,6 +321,12 @@
   </si>
   <si>
     <t>Math / Digit Manipulation / Overflow Handling</t>
+  </si>
+  <si>
+    <t>String to Integer (atoi)</t>
+  </si>
+  <si>
+    <t>Strings / Two Pointers / Digit Manipulation / Integer Overflow</t>
   </si>
 </sst>
 </file>
@@ -948,7 +954,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -973,9 +979,6 @@
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1323,7 +1326,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1920,18 +1923,32 @@
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="3">
         <v>46310</v>
       </c>
       <c r="C44" t="s">
         <v>95</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="6" t="s">
         <v>96</v>
       </c>
     </row>
+    <row r="45" spans="1:4">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46311</v>
+      </c>
+      <c r="C45" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D43" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D44" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>Day</t>
   </si>
@@ -327,6 +327,12 @@
   </si>
   <si>
     <t>Strings / Two Pointers / Digit Manipulation / Integer Overflow</t>
+  </si>
+  <si>
+    <t>Palindrome Number</t>
+  </si>
+  <si>
+    <t>Math / Digit Manipulation</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1332,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1937,7 +1943,7 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="3">
         <v>46311</v>
       </c>
       <c r="C45" t="s">
@@ -1947,8 +1953,22 @@
         <v>98</v>
       </c>
     </row>
+    <row r="46" spans="1:4">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46312</v>
+      </c>
+      <c r="C46" t="s">
+        <v>99</v>
+      </c>
+      <c r="D46" t="s">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D44" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D45" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>Day</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t>Math / Digit Manipulation</t>
+  </si>
+  <si>
+    <t>3Sum — Find Triplets That Sum to Zero</t>
+  </si>
+  <si>
+    <t>Arrays / Sorting / Two Pointers</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1338,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1957,7 +1963,7 @@
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="3">
         <v>46312</v>
       </c>
       <c r="C46" t="s">
@@ -1967,8 +1973,22 @@
         <v>100</v>
       </c>
     </row>
+    <row r="47" spans="1:4">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46313</v>
+      </c>
+      <c r="C47" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D45" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D46" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>Day</t>
   </si>
@@ -339,6 +339,12 @@
   </si>
   <si>
     <t>Arrays / Sorting / Two Pointers</t>
+  </si>
+  <si>
+    <t>Letter Combinations of a Phone Number</t>
+  </si>
+  <si>
+    <t>Strings / Hash Map / Nested Loops / Combinatorics</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1344,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1977,7 +1983,7 @@
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="3">
         <v>46313</v>
       </c>
       <c r="C47" t="s">
@@ -1987,8 +1993,22 @@
         <v>102</v>
       </c>
     </row>
+    <row r="48" spans="1:4">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8">
+        <v>46314</v>
+      </c>
+      <c r="C48" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D46" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D47" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>Day</t>
   </si>
@@ -345,6 +345,12 @@
   </si>
   <si>
     <t>Strings / Hash Map / Nested Loops / Combinatorics</t>
+  </si>
+  <si>
+    <t>Generate Parentheses</t>
+  </si>
+  <si>
+    <t>Strings / Recursion / Backtracking</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1350,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1997,7 +2003,7 @@
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="3">
         <v>46314</v>
       </c>
       <c r="C48" t="s">
@@ -2007,8 +2013,22 @@
         <v>104</v>
       </c>
     </row>
+    <row r="49" spans="1:4">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8">
+        <v>46315</v>
+      </c>
+      <c r="C49" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D47" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D48" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>Day</t>
   </si>
@@ -351,6 +351,12 @@
   </si>
   <si>
     <t>Strings / Recursion / Backtracking</t>
+  </si>
+  <si>
+    <t>Search in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>Binary Search / Searching / Array</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1356,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2017,7 +2023,7 @@
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="3">
         <v>46315</v>
       </c>
       <c r="C49" t="s">
@@ -2027,8 +2033,22 @@
         <v>106</v>
       </c>
     </row>
+    <row r="50" spans="1:4">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="8">
+        <v>46316</v>
+      </c>
+      <c r="C50" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D48" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D49" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>Day</t>
   </si>
@@ -357,6 +357,12 @@
   </si>
   <si>
     <t>Binary Search / Searching / Array</t>
+  </si>
+  <si>
+    <t>Find Minimum in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>Binary Search</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2037,7 +2043,7 @@
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="3">
         <v>46316</v>
       </c>
       <c r="C50" t="s">
@@ -2047,8 +2053,22 @@
         <v>108</v>
       </c>
     </row>
+    <row r="51" spans="1:4">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8">
+        <v>46317</v>
+      </c>
+      <c r="C51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D49" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D50" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>Day</t>
   </si>
@@ -363,6 +363,12 @@
   </si>
   <si>
     <t>Binary Search</t>
+  </si>
+  <si>
+    <t>Search a 2D Matrix</t>
+  </si>
+  <si>
+    <t>Linear Search</t>
   </si>
 </sst>
 </file>
@@ -990,7 +996,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1016,6 +1022,7 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1362,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2057,7 +2064,7 @@
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="3">
         <v>46317</v>
       </c>
       <c r="C51" t="s">
@@ -2067,8 +2074,22 @@
         <v>110</v>
       </c>
     </row>
+    <row r="52" spans="1:4">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="8">
+        <v>46318</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D50" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D51" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800"/>
+    <workbookView windowWidth="19200" windowHeight="6080"/>
   </bookViews>
   <sheets>
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <si>
     <t>Day</t>
   </si>
@@ -369,6 +369,23 @@
   </si>
   <si>
     <t>Linear Search</t>
+  </si>
+  <si>
+    <t>Divide Two Integer</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Bit Manipulation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -382,7 +399,7 @@
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -546,6 +563,12 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1019,10 +1042,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1369,7 +1392,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2078,18 +2101,32 @@
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="3">
         <v>46318</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="8" t="s">
         <v>111</v>
       </c>
       <c r="D52" t="s">
         <v>112</v>
       </c>
     </row>
+    <row r="53" spans="1:4">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="9">
+        <v>46319</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D51" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D52" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6080"/>
+    <workbookView windowWidth="19200" windowHeight="6800"/>
   </bookViews>
   <sheets>
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -375,6 +375,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve"> Bit Manipulation</t>
     </r>
     <r>
@@ -1392,7 +1398,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2115,7 +2121,7 @@
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="3">
         <v>46319</v>
       </c>
       <c r="C53" s="8" t="s">
@@ -2125,8 +2131,16 @@
         <v>114</v>
       </c>
     </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="9">
+        <v>46320</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D52" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D53" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="116">
   <si>
     <t>Day</t>
   </si>
@@ -392,6 +392,9 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
+  </si>
+  <si>
+    <t>Find First and Last Position of Element in Sorted Array</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1401,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2135,12 +2138,24 @@
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="9">
-        <v>46320</v>
+      <c r="B54" s="3"/>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="9">
+        <v>46321</v>
+      </c>
+      <c r="C55" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D53" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D54" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="118">
   <si>
     <t>Day</t>
   </si>
@@ -395,6 +395,12 @@
   </si>
   <si>
     <t>Find First and Last Position of Element in Sorted Array</t>
+  </si>
+  <si>
+    <t>Container With Most Water</t>
+  </si>
+  <si>
+    <t>Array / Two pointer</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1407,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2144,7 +2150,7 @@
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="3">
         <v>46321</v>
       </c>
       <c r="C55" t="s">
@@ -2154,8 +2160,22 @@
         <v>112</v>
       </c>
     </row>
+    <row r="56" spans="1:4">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="9">
+        <v>46322</v>
+      </c>
+      <c r="C56" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D54" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D55" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="119">
   <si>
     <t>Day</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>Array / Two pointer</t>
+  </si>
+  <si>
+    <t>Array / Prefix and Suffix Product</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1410,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2164,7 +2167,7 @@
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="3">
         <v>46322</v>
       </c>
       <c r="C56" t="s">
@@ -2174,8 +2177,22 @@
         <v>117</v>
       </c>
     </row>
+    <row r="57" spans="1:4">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="9">
+        <v>46323</v>
+      </c>
+      <c r="C57" t="s">
+        <v>89</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D55" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D56" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="121">
   <si>
     <t>Day</t>
   </si>
@@ -404,6 +404,12 @@
   </si>
   <si>
     <t>Array / Prefix and Suffix Product</t>
+  </si>
+  <si>
+    <t>Find all Numbers disappeared in an Array</t>
+  </si>
+  <si>
+    <t>Array / Hash set</t>
   </si>
 </sst>
 </file>
@@ -1410,7 +1416,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2181,7 +2187,7 @@
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="3">
         <v>46323</v>
       </c>
       <c r="C57" t="s">
@@ -2191,8 +2197,22 @@
         <v>118</v>
       </c>
     </row>
+    <row r="58" spans="1:4">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="9">
+        <v>46324</v>
+      </c>
+      <c r="C58" t="s">
+        <v>119</v>
+      </c>
+      <c r="D58" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D56" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D57" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="123">
   <si>
     <t>Day</t>
   </si>
@@ -410,6 +410,12 @@
   </si>
   <si>
     <t>Array / Hash set</t>
+  </si>
+  <si>
+    <t>Longest Subarray of 1's After Deleting One Element</t>
+  </si>
+  <si>
+    <t>Array / Sliding Window</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1422,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2201,7 +2207,7 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="3">
         <v>46324</v>
       </c>
       <c r="C58" t="s">
@@ -2211,8 +2217,22 @@
         <v>120</v>
       </c>
     </row>
+    <row r="59" spans="1:4">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="9">
+        <v>46325</v>
+      </c>
+      <c r="C59" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D57" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D58" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DSA_Journey_Metadata.xlsx
+++ b/DSA_Journey_Metadata.xlsx
@@ -10,7 +10,7 @@
     <sheet name="DSA Metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DSA Metadata'!$A$1:$D$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="125">
   <si>
     <t>Day</t>
   </si>
@@ -416,6 +416,12 @@
   </si>
   <si>
     <t>Array / Sliding Window</t>
+  </si>
+  <si>
+    <t>Subarray Sum Equals K</t>
+  </si>
+  <si>
+    <t>Array / Prefix Sum / Hash Map</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1428,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2221,7 +2227,7 @@
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="9">
+      <c r="B59" s="3">
         <v>46325</v>
       </c>
       <c r="C59" t="s">
@@ -2231,8 +2237,22 @@
         <v>122</v>
       </c>
     </row>
+    <row r="60" spans="1:4">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="9">
+        <v>46326</v>
+      </c>
+      <c r="C60" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" t="s">
+        <v>124</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D58" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D59" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
